--- a/JG-DISTRIBUIDORA/assets/inventario.xlsx
+++ b/JG-DISTRIBUIDORA/assets/inventario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bfe2c87cad12b0/IA/CLIENTES/JG DISTRIBUIDORA/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bfe2c87cad12b0/IA/CLIENTES/JG-DISTRIBUIDORA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{C781E2F5-1B3F-4D99-BE64-D4752A9B783A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CFA2FB7-17BB-4752-A003-715F8078E758}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8F997CB6-7502-455B-AFBC-A144335DDAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41FE296F-2859-43E0-8780-7D9B578F8AA8}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11295" xr2:uid="{BD69F55F-F141-4F49-9A27-303517DA3BDE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD69F55F-F141-4F49-9A27-303517DA3BDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Perfumes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="275">
   <si>
     <t>NUMERO</t>
   </si>
@@ -243,9 +243,6 @@
     <t>JUEGO DE ESPADAS</t>
   </si>
   <si>
-    <t>ERBA PURA FERJOFF</t>
-  </si>
-  <si>
     <t>BHARARA KING</t>
   </si>
   <si>
@@ -267,9 +264,6 @@
     <t>Unisex</t>
   </si>
   <si>
-    <t>C. N° 5 CLASSI</t>
-  </si>
-  <si>
     <t xml:space="preserve">DELILAH </t>
   </si>
   <si>
@@ -297,18 +291,9 @@
     <t>Versace</t>
   </si>
   <si>
-    <t>Winner Sport</t>
-  </si>
-  <si>
     <t>Esika</t>
   </si>
   <si>
-    <t>Dorsay</t>
-  </si>
-  <si>
-    <t>Solo</t>
-  </si>
-  <si>
     <t>360°</t>
   </si>
   <si>
@@ -321,12 +306,6 @@
     <t>Jean Paul Gautier</t>
   </si>
   <si>
-    <t>Nautica Voyage</t>
-  </si>
-  <si>
-    <t>Dissey Pour Homme</t>
-  </si>
-  <si>
     <t>Cloud</t>
   </si>
   <si>
@@ -351,62 +330,545 @@
     <t>ROYAL AMBER</t>
   </si>
   <si>
-    <t>Velve Gold</t>
-  </si>
-  <si>
     <t>REFERENCIA</t>
   </si>
   <si>
-    <t>PRECIO</t>
-  </si>
-  <si>
     <t>DISPONIBLE</t>
   </si>
   <si>
     <t>S</t>
   </si>
   <si>
-    <t>Ultra Male</t>
-  </si>
-  <si>
     <t>BVLGARI</t>
   </si>
   <si>
-    <t>Marine BVLGARI</t>
-  </si>
-  <si>
-    <t>Agua de BVLGARY</t>
-  </si>
-  <si>
-    <t>Pour Homme</t>
-  </si>
-  <si>
     <t>Nautica</t>
   </si>
   <si>
     <t>Lattafa</t>
   </si>
   <si>
-    <t>Kahmrah</t>
-  </si>
-  <si>
-    <t>Amethyste</t>
-  </si>
-  <si>
-    <t>Pink to Pink</t>
-  </si>
-  <si>
-    <t>Noble Blush</t>
-  </si>
-  <si>
-    <t>Musuman White Intense</t>
+    <t>Cannel</t>
+  </si>
+  <si>
+    <t>Escada</t>
+  </si>
+  <si>
+    <t>Maison Alhanbra</t>
+  </si>
+  <si>
+    <t>Carolina Herrera</t>
+  </si>
+  <si>
+    <t>Paris Hilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moschino </t>
+  </si>
+  <si>
+    <t>Burberry</t>
+  </si>
+  <si>
+    <t>Perry Ellis</t>
+  </si>
+  <si>
+    <t>Ralph Lauren</t>
+  </si>
+  <si>
+    <t>Britney Spears</t>
+  </si>
+  <si>
+    <t>Bath and body works</t>
+  </si>
+  <si>
+    <t>Victorias secret</t>
+  </si>
+  <si>
+    <t>Lancome</t>
+  </si>
+  <si>
+    <t>Tommy Hilfiger</t>
+  </si>
+  <si>
+    <t>Givenchy</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Liz Caibone</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Armaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio Banderas </t>
+  </si>
+  <si>
+    <t>Afnan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristian Dior </t>
+  </si>
+  <si>
+    <t>Paco Rabanne</t>
+  </si>
+  <si>
+    <t>Mont blanc</t>
+  </si>
+  <si>
+    <t>Dumont</t>
+  </si>
+  <si>
+    <t>Rasasi</t>
+  </si>
+  <si>
+    <t>Laurent</t>
+  </si>
+  <si>
+    <t>Lattafa by</t>
+  </si>
+  <si>
+    <t>Hugo Boss</t>
+  </si>
+  <si>
+    <t>Creed</t>
+  </si>
+  <si>
+    <t>Mochino</t>
+  </si>
+  <si>
+    <t>Maluma</t>
+  </si>
+  <si>
+    <t>Lacoste</t>
+  </si>
+  <si>
+    <t>Clinique</t>
+  </si>
+  <si>
+    <t>Victorinox</t>
+  </si>
+  <si>
+    <t>Bharara</t>
+  </si>
+  <si>
+    <t>Belleza Express</t>
+  </si>
+  <si>
+    <t>Xerjoff</t>
+  </si>
+  <si>
+    <t>Emirato</t>
+  </si>
+  <si>
+    <t>Aramain</t>
+  </si>
+  <si>
+    <t>Tom Ford</t>
+  </si>
+  <si>
+    <t>Louis Vuitton</t>
+  </si>
+  <si>
+    <t>Maison Frances</t>
+  </si>
+  <si>
+    <t>Montale</t>
+  </si>
+  <si>
+    <t>Emper</t>
+  </si>
+  <si>
+    <t>Parfums de Marly</t>
+  </si>
+  <si>
+    <t>Jomilano</t>
+  </si>
+  <si>
+    <t>ERBA PURA XERJOFF</t>
+  </si>
+  <si>
+    <t>Calvin Klein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannel N° 5 </t>
+  </si>
+  <si>
+    <t>VELVE GOLD</t>
+  </si>
+  <si>
+    <t>MUSUMAN  WHITE INTENSE</t>
+  </si>
+  <si>
+    <t>NOBLE BLUSH</t>
+  </si>
+  <si>
+    <t>PINK TO PINK</t>
+  </si>
+  <si>
+    <t>AMETHYSTE</t>
+  </si>
+  <si>
+    <t>KAHMRAH</t>
+  </si>
+  <si>
+    <t>MARINE BVLGARI</t>
+  </si>
+  <si>
+    <t>AGUA DE BVLGARY</t>
+  </si>
+  <si>
+    <t>POUR HOMME</t>
+  </si>
+  <si>
+    <t>NAUTICA VOYAGE</t>
+  </si>
+  <si>
+    <t>JEAN PAUL GAURTIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRA MALE </t>
+  </si>
+  <si>
+    <t>ISSEY MIYAKE POUR HOMME</t>
+  </si>
+  <si>
+    <t>SOLO</t>
+  </si>
+  <si>
+    <t>DORSAY</t>
+  </si>
+  <si>
+    <t>WINNER SPORT</t>
+  </si>
+  <si>
+    <t>Cloud Dream</t>
+  </si>
+  <si>
+    <t>Canelle Five</t>
+  </si>
+  <si>
+    <t>Moon Glow</t>
+  </si>
+  <si>
+    <t>Next Kiss</t>
+  </si>
+  <si>
+    <t>Dalirah</t>
+  </si>
+  <si>
+    <t>Bella Queen</t>
+  </si>
+  <si>
+    <t>Royal Blush</t>
+  </si>
+  <si>
+    <t>VIP Luxe</t>
+  </si>
+  <si>
+    <t>Pink Heiress</t>
+  </si>
+  <si>
+    <t>Toy Blanc</t>
+  </si>
+  <si>
+    <t>Osadya</t>
+  </si>
+  <si>
+    <t>Yara Gold</t>
+  </si>
+  <si>
+    <t>Yara Rose</t>
+  </si>
+  <si>
+    <t>Celestia</t>
+  </si>
+  <si>
+    <t>Pink Passport</t>
+  </si>
+  <si>
+    <t>Buriel</t>
+  </si>
+  <si>
+    <t>360 Fresh</t>
+  </si>
+  <si>
+    <t>Royal Lauren</t>
+  </si>
+  <si>
+    <t>Sweet Fantasy</t>
+  </si>
+  <si>
+    <t>Rosso Sorbet</t>
+  </si>
+  <si>
+    <t>Crazy For You</t>
+  </si>
+  <si>
+    <t>Miyake Essence</t>
+  </si>
+  <si>
+    <t>Secret Bomb</t>
+  </si>
+  <si>
+    <t>Bella Vita</t>
+  </si>
+  <si>
+    <t>Tom Legend</t>
+  </si>
+  <si>
+    <t>Golden Angel</t>
+  </si>
+  <si>
+    <t>Blue Essence</t>
+  </si>
+  <si>
+    <t>Curvex</t>
+  </si>
+  <si>
+    <t>Diesel Energy</t>
+  </si>
+  <si>
+    <t>Blue Attraction</t>
+  </si>
+  <si>
+    <t>Night PM</t>
+  </si>
+  <si>
+    <t>360 Black</t>
+  </si>
+  <si>
+    <t>Blue Denim</t>
+  </si>
+  <si>
+    <t>Eros Fire</t>
+  </si>
+  <si>
+    <t>Fresh Vibe</t>
+  </si>
+  <si>
+    <t>Fahrenheit Black</t>
+  </si>
+  <si>
+    <t>Dorset</t>
+  </si>
+  <si>
+    <t>Solo One</t>
+  </si>
+  <si>
+    <t>Wild Odyssey</t>
+  </si>
+  <si>
+    <t>Spectra Noir</t>
+  </si>
+  <si>
+    <t>Mandarin Odyssey</t>
+  </si>
+  <si>
+    <t>Miyake Intense</t>
+  </si>
+  <si>
+    <t>Miyake Pure</t>
+  </si>
+  <si>
+    <t>Black Excess</t>
+  </si>
+  <si>
+    <t>Legend Midnight</t>
+  </si>
+  <si>
+    <t>Nitro Flame</t>
+  </si>
+  <si>
+    <t>Club Night</t>
+  </si>
+  <si>
+    <t>Tropical Waves</t>
+  </si>
+  <si>
+    <t>Ultra Night</t>
+  </si>
+  <si>
+    <t>Jean Gold</t>
+  </si>
+  <si>
+    <t>Saint M7</t>
+  </si>
+  <si>
+    <t>Ocean Voyage</t>
+  </si>
+  <si>
+    <t>Bvlgari Homme</t>
+  </si>
+  <si>
+    <t>Aqua Bvlgari</t>
+  </si>
+  <si>
+    <t>Marine Aqua</t>
+  </si>
+  <si>
+    <t>Oud Glory</t>
+  </si>
+  <si>
+    <t>Orange Hugo</t>
+  </si>
+  <si>
+    <t>Avento Creed</t>
+  </si>
+  <si>
+    <t>Blue Given</t>
+  </si>
+  <si>
+    <t>Toy Two</t>
+  </si>
+  <si>
+    <t>Garnet Maluma</t>
+  </si>
+  <si>
+    <t>Asaad Gold</t>
+  </si>
+  <si>
+    <t>Bourbon Asaad</t>
+  </si>
+  <si>
+    <t>Lucky Million</t>
+  </si>
+  <si>
+    <t>Night Walker</t>
+  </si>
+  <si>
+    <t>Swiss Power</t>
+  </si>
+  <si>
+    <t>Red Lacoste</t>
+  </si>
+  <si>
+    <t>White Lacoste</t>
+  </si>
+  <si>
+    <t>Tom Classic</t>
+  </si>
+  <si>
+    <t>Happy Clinique</t>
+  </si>
+  <si>
+    <t>Victor Invictus</t>
+  </si>
+  <si>
+    <t>VIP Black Gold</t>
+  </si>
+  <si>
+    <t>VIP Secret</t>
+  </si>
+  <si>
+    <t>Khamrah Gold</t>
+  </si>
+  <si>
+    <t>Purple Amethyst</t>
+  </si>
+  <si>
+    <t>Pink Bloom</t>
+  </si>
+  <si>
+    <t>Blush Velvet</t>
+  </si>
+  <si>
+    <t>White Intense</t>
+  </si>
+  <si>
+    <t>Alexandria Royal</t>
+  </si>
+  <si>
+    <t>Saffron Oud</t>
+  </si>
+  <si>
+    <t>Velvet Gold</t>
+  </si>
+  <si>
+    <t>Azure Dream</t>
+  </si>
+  <si>
+    <t>Amber Flame</t>
+  </si>
+  <si>
+    <t>Amber Noir Luxe</t>
+  </si>
+  <si>
+    <t>Royal Gold Amber</t>
+  </si>
+  <si>
+    <t>Fujair Essence</t>
+  </si>
+  <si>
+    <t>Amber Oud Royal</t>
+  </si>
+  <si>
+    <t>Gold Oud</t>
+  </si>
+  <si>
+    <t>Night Milestone</t>
+  </si>
+  <si>
+    <t>Leather Noir 16</t>
+  </si>
+  <si>
+    <t>Nomad Shadow</t>
+  </si>
+  <si>
+    <t>Rouge Crystal</t>
+  </si>
+  <si>
+    <t>Cafe Intense</t>
+  </si>
+  <si>
+    <t>Rebel Night</t>
+  </si>
+  <si>
+    <t>Stallion Black</t>
+  </si>
+  <si>
+    <t>Malachite Sceptre</t>
+  </si>
+  <si>
+    <t>Layton Royal</t>
+  </si>
+  <si>
+    <t>Honor Glory</t>
+  </si>
+  <si>
+    <t>Sword Game</t>
+  </si>
+  <si>
+    <t>Pure Erba</t>
+  </si>
+  <si>
+    <t>CK Be One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE </t>
+  </si>
+  <si>
+    <t>Aruu Gold</t>
+  </si>
+  <si>
+    <t>Roge Manege</t>
+  </si>
+  <si>
+    <t>Kin Bharara</t>
+  </si>
+  <si>
+    <t>Sport Win</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,8 +896,15 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,12 +919,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -491,55 +972,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,23 +1093,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -895,1762 +1415,2133 @@
   <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="12" t="s">
-        <v>108</v>
+      <c r="E2" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="6" t="s">
-        <v>108</v>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="6" t="s">
-        <v>108</v>
+      <c r="C4" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="6">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="6" t="s">
-        <v>108</v>
+      <c r="C5" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="6" t="s">
-        <v>108</v>
+      <c r="B6" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="6">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="6" t="s">
-        <v>108</v>
+      <c r="C7" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="6" t="s">
-        <v>108</v>
+      <c r="B8" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="6" t="s">
-        <v>108</v>
+      <c r="C9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="6" t="s">
+      <c r="C10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="6" t="s">
-        <v>108</v>
+      <c r="D11" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="12">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="12" t="s">
-        <v>108</v>
+      <c r="C12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="6">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="6" t="s">
-        <v>108</v>
+      <c r="B13" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="6" t="s">
-        <v>108</v>
+      <c r="D15" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="6" t="s">
-        <v>108</v>
+      <c r="C16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="6">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="6" t="s">
-        <v>108</v>
+      <c r="C17" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="6" t="s">
-        <v>108</v>
+      <c r="B18" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="6">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="6" t="s">
-        <v>108</v>
+      <c r="C19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="6" t="s">
-        <v>108</v>
+      <c r="C20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="6">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="6" t="s">
-        <v>108</v>
+      <c r="C21" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="6" t="s">
-        <v>108</v>
+      <c r="C22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="6">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="6" t="s">
-        <v>108</v>
+      <c r="C23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="6" t="s">
-        <v>108</v>
+      <c r="C24" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="6">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="6" t="s">
-        <v>108</v>
+      <c r="C25" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="6" t="s">
-        <v>108</v>
+      <c r="C26" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="6">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="6" t="s">
-        <v>108</v>
+      <c r="C27" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="6" t="s">
-        <v>108</v>
+      <c r="C28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="6">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="6" t="s">
-        <v>108</v>
+      <c r="C29" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="6" t="s">
-        <v>108</v>
+      <c r="C30" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="6">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="6" t="s">
-        <v>108</v>
+      <c r="C31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="6" t="s">
-        <v>108</v>
+      <c r="C32" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="6">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="18">
         <v>360</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="6" t="s">
-        <v>108</v>
+      <c r="C33" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="12">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="11">
+        <v>34</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="12">
-        <v>34</v>
-      </c>
-      <c r="B35" s="13" t="s">
+      <c r="C36" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="11">
+        <v>36</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="12">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="6">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="6" t="s">
-        <v>108</v>
+      <c r="C37" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="12">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="12" t="s">
-        <v>108</v>
+      <c r="B38" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="12">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>87</v>
+      <c r="B39" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="12" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="12">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="12" t="s">
-        <v>108</v>
+      <c r="B40" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="6">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="6" t="s">
-        <v>108</v>
+      <c r="C41" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="6" t="s">
-        <v>108</v>
+      <c r="C42" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="6">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="6" t="s">
-        <v>108</v>
+      <c r="C43" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="12">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="12" t="s">
-        <v>108</v>
+      <c r="B44" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="12">
+      <c r="A45" s="11">
         <v>44</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>92</v>
+      <c r="B45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="12" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="6" t="s">
-        <v>108</v>
+      <c r="C46" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="6">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="6" t="s">
-        <v>108</v>
+      <c r="C47" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="6" t="s">
-        <v>108</v>
+      <c r="C48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="6">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="6" t="s">
-        <v>108</v>
+      <c r="C49" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="6" t="s">
-        <v>108</v>
+      <c r="C50" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="12">
+      <c r="A51" s="11">
         <v>50</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>93</v>
+      <c r="B51" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="12" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="12">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="12" t="s">
-        <v>108</v>
+      <c r="B52" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="6">
+      <c r="A53" s="11">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="6" t="s">
-        <v>108</v>
+      <c r="C53" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="12">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="12" t="s">
-        <v>108</v>
+      <c r="B54" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="12">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>110</v>
+      <c r="B55" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>100</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="12" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="12">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="12" t="s">
-        <v>108</v>
+      <c r="B56" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="12">
+      <c r="A57" s="11">
         <v>56</v>
       </c>
-      <c r="B57" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>110</v>
+      <c r="B57" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>100</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="12" t="s">
-        <v>108</v>
+        <v>73</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="11"/>
-      <c r="F58" s="6" t="s">
-        <v>108</v>
+      <c r="C58" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="6">
+      <c r="A59" s="11">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="6" t="s">
-        <v>108</v>
+      <c r="C59" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" s="11"/>
-      <c r="F60" s="6" t="s">
-        <v>108</v>
+      <c r="C60" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="6">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="6" t="s">
-        <v>108</v>
+      <c r="C61" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="11"/>
-      <c r="F62" s="6" t="s">
-        <v>108</v>
+      <c r="C62" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="6">
+      <c r="A63" s="11">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E63" s="11"/>
-      <c r="F63" s="6" t="s">
-        <v>108</v>
+      <c r="C63" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="6" t="s">
-        <v>108</v>
+      <c r="C64" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="6">
+      <c r="A65" s="11">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="11"/>
-      <c r="F65" s="6" t="s">
-        <v>108</v>
+      <c r="C65" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="6" t="s">
-        <v>108</v>
+      <c r="C66" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="6">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="6" t="s">
-        <v>108</v>
+      <c r="C67" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="6" t="s">
-        <v>108</v>
+      <c r="C68" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="6">
+      <c r="A69" s="11">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E69" s="11"/>
-      <c r="F69" s="6" t="s">
-        <v>108</v>
+      <c r="C69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="6" t="s">
-        <v>108</v>
+      <c r="C70" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="6">
+      <c r="A71" s="11">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="6" t="s">
-        <v>108</v>
+      <c r="C71" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="6" t="s">
-        <v>108</v>
+      <c r="C72" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="6">
+      <c r="A73" s="11">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E73" s="11"/>
-      <c r="F73" s="6" t="s">
-        <v>108</v>
+      <c r="C73" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2" t="s">
+      <c r="C74" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="11">
         <v>74</v>
       </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="6">
+      <c r="B75" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="6">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2" t="s">
+      <c r="E76" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="11">
+        <v>76</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="12">
-        <v>75</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="12">
-        <v>76</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="12" t="s">
-        <v>108</v>
+      <c r="E77" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="12">
+      <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="12" t="s">
-        <v>108</v>
+      <c r="B78" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="12">
+      <c r="A79" s="11">
         <v>78</v>
       </c>
-      <c r="B79" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>115</v>
+      <c r="B79" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="12" t="s">
-        <v>108</v>
+        <v>74</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="12">
+      <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="12" t="s">
-        <v>108</v>
+      <c r="B80" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="6">
+      <c r="A81" s="11">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="6" t="s">
-        <v>108</v>
+      <c r="C81" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E82" s="11"/>
-      <c r="F82" s="6" t="s">
-        <v>108</v>
+      <c r="C82" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="6">
+      <c r="A83" s="11">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E83" s="11"/>
-      <c r="F83" s="6" t="s">
-        <v>108</v>
+      <c r="C83" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="12">
+      <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E84" s="15"/>
-      <c r="F84" s="12" t="s">
-        <v>108</v>
+      <c r="B84" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="12">
+      <c r="A85" s="11">
         <v>84</v>
       </c>
-      <c r="B85" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>99</v>
+      <c r="B85" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85" s="15"/>
-      <c r="F85" s="12" t="s">
-        <v>108</v>
+        <v>74</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="12">
+      <c r="A86" s="6">
         <v>85</v>
       </c>
-      <c r="B86" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E86" s="15"/>
-      <c r="F86" s="12" t="s">
-        <v>108</v>
+      <c r="B86" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="12">
+      <c r="A87" s="11">
         <v>86</v>
       </c>
-      <c r="B87" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>99</v>
+      <c r="B87" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="12" t="s">
-        <v>108</v>
+        <v>74</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="12">
+      <c r="A88" s="6">
         <v>87</v>
       </c>
-      <c r="B88" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="12" t="s">
-        <v>108</v>
+      <c r="B88" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="6">
+      <c r="A89" s="11">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E89" s="11"/>
-      <c r="F89" s="6" t="s">
-        <v>108</v>
+      <c r="C89" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="6">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="6" t="s">
-        <v>108</v>
+      <c r="C90" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="6">
+      <c r="A91" s="11">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="6" t="s">
-        <v>108</v>
+      <c r="C91" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="6">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="6" t="s">
-        <v>108</v>
+      <c r="C92" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="6">
+      <c r="A93" s="11">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E93" s="11"/>
-      <c r="F93" s="6" t="s">
-        <v>108</v>
+      <c r="C93" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="6">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="6" t="s">
-        <v>108</v>
+      <c r="C94" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="6">
+      <c r="A95" s="11">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="6" t="s">
-        <v>108</v>
+      <c r="C95" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="6">
         <v>95</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E96" s="11"/>
-      <c r="F96" s="6" t="s">
-        <v>108</v>
+      <c r="C96" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="6">
+      <c r="A97" s="11">
         <v>96</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E97" s="11"/>
-      <c r="F97" s="6" t="s">
-        <v>108</v>
+      <c r="C97" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="6">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="6" t="s">
-        <v>108</v>
+      <c r="C98" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="6">
+      <c r="A99" s="11">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="6" t="s">
-        <v>108</v>
+      <c r="C99" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="6">
         <v>99</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="6" t="s">
-        <v>108</v>
+      <c r="C100" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="6">
+      <c r="A101" s="11">
         <v>100</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="6" t="s">
-        <v>108</v>
+      <c r="C101" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="6">
         <v>101</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E102" s="11"/>
-      <c r="F102" s="6" t="s">
-        <v>108</v>
+      <c r="C102" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="6">
+      <c r="A103" s="11">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E103" s="11"/>
-      <c r="F103" s="6" t="s">
-        <v>108</v>
+      <c r="C103" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="6">
         <v>103</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="11">
+        <v>104</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105" s="6">
-        <v>104</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="6" t="s">
-        <v>108</v>
+      <c r="C105" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="6">
         <v>105</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E106" s="11"/>
-      <c r="F106" s="6" t="s">
-        <v>108</v>
+      <c r="B106" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
